--- a/demo/workbooks/DEMO_NIST_800-53r5_Example System.xlsx
+++ b/demo/workbooks/DEMO_NIST_800-53r5_Example System.xlsx
@@ -1022,7 +1022,7 @@
       <c r="E11" s="5" t="inlineStr"/>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>The Example System Demo workstation is hardened to the Windows Server 2022 STIG; most recent checklist dated 2026-05-18.</t>
+          <t>The Example System Demo hosts are hardened to their DISA STIGs; the RHEL 9 and Windows Server 2022 checklists are the most recent configuration baselines on record.</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1032,12 +1032,12 @@
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>CCI-000363</t>
+          <t>CCI-000366</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>The organization establishes and documents configuration settings using organization-defined security configuration checklists.</t>
+          <t>The organization implements the security configuration settings.</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="Q11" s="5" t="inlineStr">
         <is>
-          <t>Examined Windows_Server_2022_STIG_Sample.ckl dated 2026-05-18. Open findings are tracked in the POA&amp;M.</t>
+          <t>Examined RHEL_9_STIG_Sample.cklb and Windows_Server_2022_STIG_Sample.ckl. Open findings are tracked in the POA&amp;M.</t>
         </is>
       </c>
       <c r="R11" s="5" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>CCI-001067</t>
+          <t>CCI-001054</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">

--- a/demo/workbooks/DEMO_NIST_800-53r5_Example System.xlsx
+++ b/demo/workbooks/DEMO_NIST_800-53r5_Example System.xlsx
@@ -717,7 +717,7 @@
       </c>
       <c r="Q7" s="5" t="inlineStr">
         <is>
-          <t>Examined IdAM provisioning workflow export (USD20240315) and confirmed automated create/disable/remove actions are logged in the AD audit channel. Sampled three onboarding tickets; all show automated account creation.</t>
+          <t>Examined Information System Account Management Policy (USD20240315), which documents the automated AD create/disable/remove workflow; confirmed account lifecycle actions are logged in the AD audit channel. Sampled three onboarding tickets; all show automated account creation.</t>
         </is>
       </c>
       <c r="R7" s="5" t="inlineStr">
@@ -848,9 +848,17 @@
           <t>Session Lock</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr"/>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
       <c r="E9" s="5" t="inlineStr"/>
-      <c r="F9" s="5" t="inlineStr"/>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>The Default Domain Policy enforces a session lock after 15 minutes of inactivity, requiring re-authentication to resume.</t>
+        </is>
+      </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
           <t>AC-11</t>
@@ -858,7 +866,7 @@
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>CCI-000056</t>
+          <t>CCI-000057</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
@@ -882,10 +890,26 @@
         </is>
       </c>
       <c r="M9" s="5" t="inlineStr"/>
-      <c r="N9" s="5" t="inlineStr"/>
-      <c r="O9" s="5" t="inlineStr"/>
-      <c r="P9" s="5" t="inlineStr"/>
-      <c r="Q9" s="5" t="inlineStr"/>
+      <c r="N9" s="5" t="inlineStr">
+        <is>
+          <t>Compliant</t>
+        </is>
+      </c>
+      <c r="O9" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="P9" s="5" t="inlineStr">
+        <is>
+          <t>Noah Jaskolski</t>
+        </is>
+      </c>
+      <c r="Q9" s="5" t="inlineStr">
+        <is>
+          <t>Examined GPO_Password_Policy_Export.xlsx (USD20240218): 'Interactive logon: Machine inactivity limit' = '900 seconds' (15 minutes), enforcing an automatic session lock.</t>
+        </is>
+      </c>
       <c r="R9" s="5" t="inlineStr">
         <is>
           <t>NIST SP 800-53 Rev. 5</t>
@@ -893,7 +917,7 @@
       </c>
       <c r="S9" s="5" t="inlineStr">
         <is>
-          <t>System-Specific</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="T9" s="5" t="inlineStr">
@@ -927,7 +951,7 @@
       <c r="E10" s="5" t="inlineStr"/>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>The Default Domain Policy enforces a 15-character minimum and complexity per I&amp;A Procedures (USD20240212) Section 3.</t>
+          <t>The Default Domain Policy enforces a 15-character minimum password length per I&amp;A Procedures (USD20240212) Section 3.</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -937,12 +961,12 @@
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>CCI-000192</t>
+          <t>CCI-000205</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>The information system enforces minimum password complexity.</t>
+          <t>The information system enforces minimum password length.</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">

--- a/demo/workbooks/DEMO_NIST_800-53r5_Example System.xlsx
+++ b/demo/workbooks/DEMO_NIST_800-53r5_Example System.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U13"/>
+  <dimension ref="A1:U14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1230,90 +1230,165 @@
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
           <t>Inherited</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>Boundary protection is inherited from the enclosing SDA Enterprise Service per SDA Controls overlay row 412.</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>SC-7</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>CCI-001097</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>The information system monitors and controls communications at the external boundary and key internal boundaries.</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>If inheriting, cite the provider system; otherwise provide the firewall config and ACL.</t>
+        </is>
+      </c>
+      <c r="K13" s="6" t="inlineStr">
+        <is>
+          <t>Examine the inheritance memorandum or the firewall config.</t>
+        </is>
+      </c>
+      <c r="L13" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M13" s="6" t="inlineStr">
+        <is>
+          <t>SDA Enterprise Service</t>
+        </is>
+      </c>
+      <c r="N13" s="6" t="inlineStr">
+        <is>
+          <t>Compliant</t>
+        </is>
+      </c>
+      <c r="O13" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="P13" s="6" t="inlineStr">
+        <is>
+          <t>Noah Jaskolski</t>
+        </is>
+      </c>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>Boundary protection is fully inherited from the SDA Enterprise Service per SDA Controls overlay row 412. An inherited control whose provider satisfies the requirement is Compliant (applicable but met by the provider) — not Not Applicable.</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>NIST SP 800-53 Rev. 5</t>
+        </is>
+      </c>
+      <c r="S13" s="6" t="inlineStr">
         <is>
           <t>Inherited</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>Boundary protection is inherited from the enclosing SDA Enterprise Service per SDA Controls overlay row 412.</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>SC-7</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>CCI-001097</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>The information system monitors and controls communications at the external boundary and key internal boundaries.</t>
-        </is>
-      </c>
-      <c r="J13" s="6" t="inlineStr">
-        <is>
-          <t>If inheriting, cite the provider system; otherwise provide the firewall config and ACL.</t>
-        </is>
-      </c>
-      <c r="K13" s="6" t="inlineStr">
-        <is>
-          <t>Examine the inheritance memorandum or the firewall config.</t>
-        </is>
-      </c>
-      <c r="L13" s="6" t="inlineStr">
+      <c r="T13" s="6" t="inlineStr">
+        <is>
+          <t>T. Prior</t>
+        </is>
+      </c>
+      <c r="U13" s="6" t="inlineStr"/>
+    </row>
+    <row r="14" ht="110" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M13" s="6" t="inlineStr">
-        <is>
-          <t>SDA Enterprise Service</t>
-        </is>
-      </c>
-      <c r="N13" s="6" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="O13" s="6" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="P13" s="6" t="inlineStr">
-        <is>
-          <t>Noah Jaskolski</t>
-        </is>
-      </c>
-      <c r="Q13" s="6" t="inlineStr">
-        <is>
-          <t>Inheritance from SDA Enterprise Service documented in SDA Controls overlay row 412. No local boundary device implemented.</t>
-        </is>
-      </c>
-      <c r="R13" s="6" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>AC-17</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Remote Access</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr"/>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>Remote access to the Example System Demo workloads differs by cloud: the AWS GovCloud enclave uses customer-configured Client VPN with conditional access, while the Azure Government enclave brokers all administrative remote access through managed Azure Bastion.</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>AC-17</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>CCI-000063</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>The organization authorizes remote access to the information system prior to connection and enforces approved remote-access methods.</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>Provide the remote-access configuration for each cloud enclave; cite the provider-managed plane where access is inherited.</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>Examine the remote-access method per scope. For the customer-owned scope verify VPN/conditional-access enforcement; for the inherited scope confirm the managed plane covers the requirement.</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M14" s="5" t="inlineStr"/>
+      <c r="N14" s="5" t="inlineStr"/>
+      <c r="O14" s="5" t="inlineStr"/>
+      <c r="P14" s="5" t="inlineStr"/>
+      <c r="Q14" s="5" t="inlineStr"/>
+      <c r="R14" s="5" t="inlineStr">
         <is>
           <t>NIST SP 800-53 Rev. 5</t>
         </is>
       </c>
-      <c r="S13" s="6" t="inlineStr">
-        <is>
-          <t>Inherited</t>
-        </is>
-      </c>
-      <c r="T13" s="6" t="inlineStr">
+      <c r="S14" s="5" t="inlineStr">
+        <is>
+          <t>System-Specific</t>
+        </is>
+      </c>
+      <c r="T14" s="5" t="inlineStr">
         <is>
           <t>T. Prior</t>
         </is>
       </c>
-      <c r="U13" s="6" t="inlineStr"/>
+      <c r="U14" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1321,7 +1396,7 @@
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="N7:N13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid status" error="Status must be Compliant, Non-Compliant, or Not Applicable." type="list">
+    <dataValidation sqref="N7:N14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid status" error="Status must be Compliant, Non-Compliant, or Not Applicable." type="list">
       <formula1>"Compliant,Non-Compliant,Not Applicable"</formula1>
     </dataValidation>
   </dataValidations>

--- a/demo/workbooks/DEMO_NIST_800-53r5_Example System.xlsx
+++ b/demo/workbooks/DEMO_NIST_800-53r5_Example System.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U14"/>
+  <dimension ref="A1:U15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1390,13 +1390,104 @@
       </c>
       <c r="U14" s="5" t="inlineStr"/>
     </row>
+    <row r="15" ht="110" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>AC-18</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Wireless Access</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr"/>
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>The Example System Demo authorization boundary contains no wireless networking. All connectivity is wired within the data center enclave; wireless is not deployed and is prohibited by the system configuration baseline.</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>AC-18</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>CCI-001438</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>The organization establishes configuration requirements and authorizes wireless access to the information system.</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>If wireless is present, provide the wireless configuration; otherwise document the scope exclusion.</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>Confirm the boundary has no wireless components. Verify the scope-exclusion statement in the SSP.</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M15" s="5" t="inlineStr"/>
+      <c r="N15" s="5" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="O15" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="P15" s="5" t="inlineStr">
+        <is>
+          <t>Noah Jaskolski</t>
+        </is>
+      </c>
+      <c r="Q15" s="5" t="inlineStr">
+        <is>
+          <t>Not Applicable — the Example System Demo boundary deploys no wireless networking; all access is wired within the data-center enclave. Wireless is prohibited by the configuration baseline, so AC-18 does not apply to this system.</t>
+        </is>
+      </c>
+      <c r="R15" s="5" t="inlineStr">
+        <is>
+          <t>NIST SP 800-53 Rev. 5</t>
+        </is>
+      </c>
+      <c r="S15" s="5" t="inlineStr">
+        <is>
+          <t>System-Specific</t>
+        </is>
+      </c>
+      <c r="T15" s="5" t="inlineStr">
+        <is>
+          <t>T. Prior</t>
+        </is>
+      </c>
+      <c r="U15" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A5:U5"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="N7:N14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid status" error="Status must be Compliant, Non-Compliant, or Not Applicable." type="list">
+    <dataValidation sqref="N7:N15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid status" error="Status must be Compliant, Non-Compliant, or Not Applicable." type="list">
       <formula1>"Compliant,Non-Compliant,Not Applicable"</formula1>
     </dataValidation>
   </dataValidations>

--- a/demo/workbooks/DEMO_NIST_800-53r5_Example System.xlsx
+++ b/demo/workbooks/DEMO_NIST_800-53r5_Example System.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U15"/>
+  <dimension ref="A1:U17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1481,13 +1481,163 @@
       </c>
       <c r="U15" s="5" t="inlineStr"/>
     </row>
+    <row r="16" ht="110" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>PE-3</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Physical Access Control</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr"/>
+      <c r="E16" s="5" t="inlineStr"/>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>Physical access control for the Example System Demo workloads is inherited from the cloud service providers: AWS GovCloud and Azure Government operate the datacenter physical-security plane (multi-factor perimeter access, biometric server-room boundaries, mantrap vestibules, 24x7 guards).</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>PE-3</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>CCI-000919</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>The organization enforces physical access authorizations at entry and exit points to the facility where the information system resides.</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>If inheriting, cite the provider CRM; otherwise provide the facility physical-access procedures and access logs.</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>Examine the provider CRM inheritance for each cloud enclave. Confirm the datacenter physical-access plane is provider-owned.</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M16" s="5" t="inlineStr"/>
+      <c r="N16" s="5" t="inlineStr"/>
+      <c r="O16" s="5" t="inlineStr"/>
+      <c r="P16" s="5" t="inlineStr"/>
+      <c r="Q16" s="5" t="inlineStr"/>
+      <c r="R16" s="5" t="inlineStr">
+        <is>
+          <t>NIST SP 800-53 Rev. 5</t>
+        </is>
+      </c>
+      <c r="S16" s="5" t="inlineStr">
+        <is>
+          <t>System-Specific</t>
+        </is>
+      </c>
+      <c r="T16" s="5" t="inlineStr">
+        <is>
+          <t>T. Prior</t>
+        </is>
+      </c>
+      <c r="U16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17" ht="110" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>AU-4</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Audit Log Storage Capacity</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr"/>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>Audit log storage capacity for the Example System Demo SIEM tier is documented in the Audit Log Storage Capacity Memo (USD20240623). The memo is a draft whose capacity sections are not yet reconciled.</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>AU-4</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>CCI-000137</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>The organization allocates audit log storage capacity to accommodate the organization-defined audit log retention requirements.</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>Provide the audit storage capacity allocation and a utilization analysis demonstrating the retention period is met.</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>Examine the allocated capacity against the 1-year retention requirement and the measured ingest/utilization rate.</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M17" s="5" t="inlineStr"/>
+      <c r="N17" s="5" t="inlineStr"/>
+      <c r="O17" s="5" t="inlineStr"/>
+      <c r="P17" s="5" t="inlineStr"/>
+      <c r="Q17" s="5" t="inlineStr"/>
+      <c r="R17" s="5" t="inlineStr">
+        <is>
+          <t>NIST SP 800-53 Rev. 5</t>
+        </is>
+      </c>
+      <c r="S17" s="5" t="inlineStr">
+        <is>
+          <t>System-Specific</t>
+        </is>
+      </c>
+      <c r="T17" s="5" t="inlineStr">
+        <is>
+          <t>T. Prior</t>
+        </is>
+      </c>
+      <c r="U17" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A5:U5"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="N7:N15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid status" error="Status must be Compliant, Non-Compliant, or Not Applicable." type="list">
+    <dataValidation sqref="N7:N17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid status" error="Status must be Compliant, Non-Compliant, or Not Applicable." type="list">
       <formula1>"Compliant,Non-Compliant,Not Applicable"</formula1>
     </dataValidation>
   </dataValidations>

--- a/demo/workbooks/DEMO_NIST_800-53r5_Example System.xlsx
+++ b/demo/workbooks/DEMO_NIST_800-53r5_Example System.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U17"/>
+  <dimension ref="A1:U19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1631,13 +1631,163 @@
       </c>
       <c r="U17" s="5" t="inlineStr"/>
     </row>
+    <row r="18" ht="110" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>AU-6</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Audit Record Review, Analysis, and Reporting</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>Audit record review for the Example System Demo differs by cloud: the AWS GovCloud enclave shares review between the provider SOC and the customer, while the Azure Government enclave is reviewed end-to-end by the customer's Microsoft Sentinel workspace.</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>AU-6</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>CCI-000148</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>The organization reviews and analyzes information system audit records for indications of inappropriate or unusual activity.</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>Provide the audit-review cadence and sample findings for each cloud enclave; cite the provider-shared review where applicable.</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>Examine the audit-review process per scope. For the customer-owned scope verify the SIEM review cadence; for the shared scope confirm the provider/customer review split.</t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M18" s="5" t="inlineStr"/>
+      <c r="N18" s="5" t="inlineStr"/>
+      <c r="O18" s="5" t="inlineStr"/>
+      <c r="P18" s="5" t="inlineStr"/>
+      <c r="Q18" s="5" t="inlineStr"/>
+      <c r="R18" s="5" t="inlineStr">
+        <is>
+          <t>NIST SP 800-53 Rev. 5</t>
+        </is>
+      </c>
+      <c r="S18" s="5" t="inlineStr">
+        <is>
+          <t>System-Specific</t>
+        </is>
+      </c>
+      <c r="T18" s="5" t="inlineStr">
+        <is>
+          <t>T. Prior</t>
+        </is>
+      </c>
+      <c r="U18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19" ht="110" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>SC-13</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Cryptographic Protection</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr"/>
+      <c r="E19" s="5" t="inlineStr"/>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>Cryptographic protection for the Example System Demo differs by cloud: the AWS GovCloud enclave shares responsibility (customer selects FIPS endpoints and guest-OS FIPS mode), while the Azure Government enclave consumes only Microsoft-provided FIPS 140-2 validated modules and fully inherits the control.</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>SC-13</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>CCI-002450</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>The information system implements organization-defined cryptographic uses and type of cryptography in accordance with applicable laws.</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>Provide the FIPS-validated module configuration per cloud enclave; cite the provider CRM where the control is inherited.</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>Examine the cryptographic implementation per scope. For the shared scope verify FIPS endpoint/guest-OS configuration; for the inherited scope confirm the provider supplies the validated modules.</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M19" s="5" t="inlineStr"/>
+      <c r="N19" s="5" t="inlineStr"/>
+      <c r="O19" s="5" t="inlineStr"/>
+      <c r="P19" s="5" t="inlineStr"/>
+      <c r="Q19" s="5" t="inlineStr"/>
+      <c r="R19" s="5" t="inlineStr">
+        <is>
+          <t>NIST SP 800-53 Rev. 5</t>
+        </is>
+      </c>
+      <c r="S19" s="5" t="inlineStr">
+        <is>
+          <t>System-Specific</t>
+        </is>
+      </c>
+      <c r="T19" s="5" t="inlineStr">
+        <is>
+          <t>T. Prior</t>
+        </is>
+      </c>
+      <c r="U19" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A5:U5"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="N7:N17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid status" error="Status must be Compliant, Non-Compliant, or Not Applicable." type="list">
+    <dataValidation sqref="N7:N19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid status" error="Status must be Compliant, Non-Compliant, or Not Applicable." type="list">
       <formula1>"Compliant,Non-Compliant,Not Applicable"</formula1>
     </dataValidation>
   </dataValidations>

--- a/demo/workbooks/DEMO_NIST_800-53r5_Example System.xlsx
+++ b/demo/workbooks/DEMO_NIST_800-53r5_Example System.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U19"/>
+  <dimension ref="A1:U20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1781,13 +1781,88 @@
       </c>
       <c r="U19" s="5" t="inlineStr"/>
     </row>
+    <row r="20" ht="110" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>AU-9</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Protection of Audit Information</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr"/>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>Protection of audit information for the Example System Demo is customer-owned on both cloud enclaves; immutability and access controls on the customer log stores are documented in the Audit Information Protection Memo (USD20240624), a draft whose protection sections are not yet reconciled.</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>AU-9</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>CCI-001493</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>The information system protects audit information and audit tools from unauthorized access, modification, and deletion.</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>Provide the immutability / access-control configuration for the customer audit log stores on each cloud enclave.</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>Examine the configured object-lock / immutable-retention and access controls on the customer log stores against the protection requirement; confirm the as-configured state matches the memo.</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M20" s="5" t="inlineStr"/>
+      <c r="N20" s="5" t="inlineStr"/>
+      <c r="O20" s="5" t="inlineStr"/>
+      <c r="P20" s="5" t="inlineStr"/>
+      <c r="Q20" s="5" t="inlineStr"/>
+      <c r="R20" s="5" t="inlineStr">
+        <is>
+          <t>NIST SP 800-53 Rev. 5</t>
+        </is>
+      </c>
+      <c r="S20" s="5" t="inlineStr">
+        <is>
+          <t>System-Specific</t>
+        </is>
+      </c>
+      <c r="T20" s="5" t="inlineStr">
+        <is>
+          <t>T. Prior</t>
+        </is>
+      </c>
+      <c r="U20" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A5:U5"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="N7:N19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid status" error="Status must be Compliant, Non-Compliant, or Not Applicable." type="list">
+    <dataValidation sqref="N7:N20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid status" error="Status must be Compliant, Non-Compliant, or Not Applicable." type="list">
       <formula1>"Compliant,Non-Compliant,Not Applicable"</formula1>
     </dataValidation>
   </dataValidations>

--- a/demo/workbooks/DEMO_NIST_800-53r5_Example System.xlsx
+++ b/demo/workbooks/DEMO_NIST_800-53r5_Example System.xlsx
@@ -1501,7 +1501,7 @@
       <c r="E16" s="5" t="inlineStr"/>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>Physical access control for the Example System Demo workloads is inherited from the cloud service providers: AWS GovCloud and Azure Government operate the datacenter physical-security plane (multi-factor perimeter access, biometric server-room boundaries, mantrap vestibules, 24x7 guards).</t>
+          <t>Physical access control for the Example System Demo is inherited on every scope: the AWS GovCloud and Azure Government enclaves inherit datacenter physical security from the cloud service providers, and the on-premises/workbook footprint inherits physical access from the DoW Enterprise data center (Column L) — multi-factor perimeter access, biometric server-room boundaries, mantrap vestibules, 24x7 guards.</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
@@ -1521,17 +1521,17 @@
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>If inheriting, cite the provider CRM; otherwise provide the facility physical-access procedures and access logs.</t>
+          <t>If inheriting, cite the provider CRM (cloud) and the workbook inheritance source (Column L); otherwise provide the facility physical-access procedures and access logs.</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>Examine the provider CRM inheritance for each cloud enclave. Confirm the datacenter physical-access plane is provider-owned.</t>
+          <t>Examine the provider CRM inheritance for each cloud enclave and the Column L inheritance source for the flex scope. Confirm every scope's physical-access plane is inherited.</t>
         </is>
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>DoW Enterprise</t>
         </is>
       </c>
       <c r="M16" s="5" t="inlineStr"/>

--- a/demo/workbooks/DEMO_NIST_800-53r5_Example System.xlsx
+++ b/demo/workbooks/DEMO_NIST_800-53r5_Example System.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U20"/>
+  <dimension ref="A1:U22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1489,56 +1489,72 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>PE-3</t>
+          <t>PE-10</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Physical Access Control</t>
+          <t>Emergency Shutoff</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr"/>
       <c r="E16" s="5" t="inlineStr"/>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>Physical access control for the Example System Demo is inherited on every scope: the AWS GovCloud and Azure Government enclaves inherit datacenter physical security from the cloud service providers, and the on-premises/workbook footprint inherits physical access from the DoW Enterprise data center (Column L) — multi-factor perimeter access, biometric server-room boundaries, mantrap vestibules, 24x7 guards.</t>
+          <t>Emergency power shutoff for the Example System Demo is a provider-internal datacenter facility control on every cloud enclave; the system has no customer-operated facility requiring an emergency power-shutoff capability.</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>PE-3</t>
+          <t>PE-10</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>CCI-000919</t>
+          <t>CCI-000813</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>The organization enforces physical access authorizations at entry and exit points to the facility where the information system resides.</t>
+          <t>The organization provides the capability to shut off power to the information system or individual system components in emergencies.</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>If inheriting, cite the provider CRM (cloud) and the workbook inheritance source (Column L); otherwise provide the facility physical-access procedures and access logs.</t>
+          <t>If a customer-operated facility exists, provide the emergency power-shutoff procedure; otherwise document the scope exclusion.</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>Examine the provider CRM inheritance for each cloud enclave and the Column L inheritance source for the flex scope. Confirm every scope's physical-access plane is inherited.</t>
+          <t>Confirm emergency shutoff is provider-internal on every cloud and that no customer facility requires a local capability.</t>
         </is>
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>DoW Enterprise</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M16" s="5" t="inlineStr"/>
-      <c r="N16" s="5" t="inlineStr"/>
-      <c r="O16" s="5" t="inlineStr"/>
-      <c r="P16" s="5" t="inlineStr"/>
-      <c r="Q16" s="5" t="inlineStr"/>
+      <c r="N16" s="5" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="O16" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="P16" s="5" t="inlineStr">
+        <is>
+          <t>Noah Jaskolski</t>
+        </is>
+      </c>
+      <c r="Q16" s="5" t="inlineStr">
+        <is>
+          <t>Not Applicable — datacenter emergency power shutoff is a provider-internal facility control on every cloud enclave (AWS GovCloud, Azure Government) and the system operates no customer facility requiring an equivalent capability. PE-10 does not apply to any slice of this system.</t>
+        </is>
+      </c>
       <c r="R16" s="5" t="inlineStr">
         <is>
           <t>NIST SP 800-53 Rev. 5</t>
@@ -1564,44 +1580,44 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>AU-4</t>
+          <t>MP-6</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Audit Log Storage Capacity</t>
+          <t>Media Sanitization</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr"/>
       <c r="E17" s="5" t="inlineStr"/>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>Audit log storage capacity for the Example System Demo SIEM tier is documented in the Audit Log Storage Capacity Memo (USD20240623). The memo is a draft whose capacity sections are not yet reconciled.</t>
+          <t>Media sanitization for the Example System Demo differs by cloud: the AWS GovCloud enclave treats it as not applicable (provider performs cryptographic erasure of customer-managed media), while the Azure Government enclave inherits the control from the provider's media-sanitization plane.</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>AU-4</t>
+          <t>MP-6</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>CCI-000137</t>
+          <t>CCI-001028</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>The organization allocates audit log storage capacity to accommodate the organization-defined audit log retention requirements.</t>
+          <t>The organization sanitizes information system media prior to disposal, release, or reuse.</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>Provide the audit storage capacity allocation and a utilization analysis demonstrating the retention period is met.</t>
+          <t>Provide the media-sanitization procedure or the provider attestation per cloud enclave; document any scope exclusion.</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>Examine the allocated capacity against the 1-year retention requirement and the measured ingest/utilization rate.</t>
+          <t>Examine media sanitization per scope: confirm the AWS N/A exclusion and the Azure inherited coverage; assess the flex scope locally.</t>
         </is>
       </c>
       <c r="L17" s="5" t="inlineStr">
@@ -1639,49 +1655,49 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>AU-6</t>
+          <t>PE-3</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Audit Record Review, Analysis, and Reporting</t>
+          <t>Physical Access Control</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr"/>
       <c r="E18" s="5" t="inlineStr"/>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>Audit record review for the Example System Demo differs by cloud: the AWS GovCloud enclave shares review between the provider SOC and the customer, while the Azure Government enclave is reviewed end-to-end by the customer's Microsoft Sentinel workspace.</t>
+          <t>Physical access control for the Example System Demo is inherited on every scope: the AWS GovCloud and Azure Government enclaves inherit datacenter physical security from the cloud service providers, and the on-premises/workbook footprint inherits physical access from the DoW Enterprise data center (Column L) — multi-factor perimeter access, biometric server-room boundaries, mantrap vestibules, 24x7 guards.</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>AU-6</t>
+          <t>PE-3</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>CCI-000148</t>
+          <t>CCI-000919</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>The organization reviews and analyzes information system audit records for indications of inappropriate or unusual activity.</t>
+          <t>The organization enforces physical access authorizations at entry and exit points to the facility where the information system resides.</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>Provide the audit-review cadence and sample findings for each cloud enclave; cite the provider-shared review where applicable.</t>
+          <t>If inheriting, cite the provider CRM (cloud) and the workbook inheritance source (Column L); otherwise provide the facility physical-access procedures and access logs.</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>Examine the audit-review process per scope. For the customer-owned scope verify the SIEM review cadence; for the shared scope confirm the provider/customer review split.</t>
+          <t>Examine the provider CRM inheritance for each cloud enclave and the Column L inheritance source for the flex scope. Confirm every scope's physical-access plane is inherited.</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>DoW Enterprise</t>
         </is>
       </c>
       <c r="M18" s="5" t="inlineStr"/>
@@ -1714,44 +1730,44 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>SC-13</t>
+          <t>AU-4</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Cryptographic Protection</t>
+          <t>Audit Log Storage Capacity</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr"/>
       <c r="E19" s="5" t="inlineStr"/>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>Cryptographic protection for the Example System Demo differs by cloud: the AWS GovCloud enclave shares responsibility (customer selects FIPS endpoints and guest-OS FIPS mode), while the Azure Government enclave consumes only Microsoft-provided FIPS 140-2 validated modules and fully inherits the control.</t>
+          <t>Audit log storage capacity for the Example System Demo SIEM tier is documented in the Audit Log Storage Capacity Memo (USD20240623). The memo is a draft whose capacity sections are not yet reconciled.</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>SC-13</t>
+          <t>AU-4</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>CCI-002450</t>
+          <t>CCI-000137</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>The information system implements organization-defined cryptographic uses and type of cryptography in accordance with applicable laws.</t>
+          <t>The organization allocates audit log storage capacity to accommodate the organization-defined audit log retention requirements.</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>Provide the FIPS-validated module configuration per cloud enclave; cite the provider CRM where the control is inherited.</t>
+          <t>Provide the audit storage capacity allocation and a utilization analysis demonstrating the retention period is met.</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>Examine the cryptographic implementation per scope. For the shared scope verify FIPS endpoint/guest-OS configuration; for the inherited scope confirm the provider supplies the validated modules.</t>
+          <t>Examine the allocated capacity against the 1-year retention requirement and the measured ingest/utilization rate.</t>
         </is>
       </c>
       <c r="L19" s="5" t="inlineStr">
@@ -1789,44 +1805,44 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>AU-9</t>
+          <t>AU-6</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Protection of Audit Information</t>
+          <t>Audit Record Review, Analysis, and Reporting</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr"/>
       <c r="E20" s="5" t="inlineStr"/>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>Protection of audit information for the Example System Demo is customer-owned on both cloud enclaves; immutability and access controls on the customer log stores are documented in the Audit Information Protection Memo (USD20240624), a draft whose protection sections are not yet reconciled.</t>
+          <t>Audit record review for the Example System Demo differs by cloud: the AWS GovCloud enclave shares review between the provider SOC and the customer, while the Azure Government enclave is reviewed end-to-end by the customer's Microsoft Sentinel workspace.</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>AU-9</t>
+          <t>AU-6</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>CCI-001493</t>
+          <t>CCI-000148</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>The information system protects audit information and audit tools from unauthorized access, modification, and deletion.</t>
+          <t>The organization reviews and analyzes information system audit records for indications of inappropriate or unusual activity.</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>Provide the immutability / access-control configuration for the customer audit log stores on each cloud enclave.</t>
+          <t>Provide the audit-review cadence and sample findings for each cloud enclave; cite the provider-shared review where applicable.</t>
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>Examine the configured object-lock / immutable-retention and access controls on the customer log stores against the protection requirement; confirm the as-configured state matches the memo.</t>
+          <t>Examine the audit-review process per scope. For the customer-owned scope verify the SIEM review cadence; for the shared scope confirm the provider/customer review split.</t>
         </is>
       </c>
       <c r="L20" s="5" t="inlineStr">
@@ -1856,13 +1872,163 @@
       </c>
       <c r="U20" s="5" t="inlineStr"/>
     </row>
+    <row r="21" ht="110" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>SC-13</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Cryptographic Protection</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr"/>
+      <c r="E21" s="5" t="inlineStr"/>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>Cryptographic protection for the Example System Demo differs by cloud: the AWS GovCloud enclave shares responsibility (customer selects FIPS endpoints and guest-OS FIPS mode), while the Azure Government enclave consumes only Microsoft-provided FIPS 140-2 validated modules and fully inherits the control.</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>SC-13</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>CCI-002450</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>The information system implements organization-defined cryptographic uses and type of cryptography in accordance with applicable laws.</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>Provide the FIPS-validated module configuration per cloud enclave; cite the provider CRM where the control is inherited.</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>Examine the cryptographic implementation per scope. For the shared scope verify FIPS endpoint/guest-OS configuration; for the inherited scope confirm the provider supplies the validated modules.</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="inlineStr"/>
+      <c r="N21" s="5" t="inlineStr"/>
+      <c r="O21" s="5" t="inlineStr"/>
+      <c r="P21" s="5" t="inlineStr"/>
+      <c r="Q21" s="5" t="inlineStr"/>
+      <c r="R21" s="5" t="inlineStr">
+        <is>
+          <t>NIST SP 800-53 Rev. 5</t>
+        </is>
+      </c>
+      <c r="S21" s="5" t="inlineStr">
+        <is>
+          <t>System-Specific</t>
+        </is>
+      </c>
+      <c r="T21" s="5" t="inlineStr">
+        <is>
+          <t>T. Prior</t>
+        </is>
+      </c>
+      <c r="U21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22" ht="110" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>AU-9</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Protection of Audit Information</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr"/>
+      <c r="E22" s="5" t="inlineStr"/>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>Protection of audit information for the Example System Demo is customer-owned on both cloud enclaves; immutability and access controls on the customer log stores are documented in the Audit Information Protection Memo (USD20240624), a draft whose protection sections are not yet reconciled.</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>AU-9</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>CCI-001493</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>The information system protects audit information and audit tools from unauthorized access, modification, and deletion.</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>Provide the immutability / access-control configuration for the customer audit log stores on each cloud enclave.</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>Examine the configured object-lock / immutable-retention and access controls on the customer log stores against the protection requirement; confirm the as-configured state matches the memo.</t>
+        </is>
+      </c>
+      <c r="L22" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M22" s="5" t="inlineStr"/>
+      <c r="N22" s="5" t="inlineStr"/>
+      <c r="O22" s="5" t="inlineStr"/>
+      <c r="P22" s="5" t="inlineStr"/>
+      <c r="Q22" s="5" t="inlineStr"/>
+      <c r="R22" s="5" t="inlineStr">
+        <is>
+          <t>NIST SP 800-53 Rev. 5</t>
+        </is>
+      </c>
+      <c r="S22" s="5" t="inlineStr">
+        <is>
+          <t>System-Specific</t>
+        </is>
+      </c>
+      <c r="T22" s="5" t="inlineStr">
+        <is>
+          <t>T. Prior</t>
+        </is>
+      </c>
+      <c r="U22" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A5:U5"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="N7:N20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid status" error="Status must be Compliant, Non-Compliant, or Not Applicable." type="list">
+    <dataValidation sqref="N7:N22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid status" error="Status must be Compliant, Non-Compliant, or Not Applicable." type="list">
       <formula1>"Compliant,Non-Compliant,Not Applicable"</formula1>
     </dataValidation>
   </dataValidations>

--- a/demo/workbooks/DEMO_NIST_800-53r5_Example System.xlsx
+++ b/demo/workbooks/DEMO_NIST_800-53r5_Example System.xlsx
@@ -1697,10 +1697,14 @@
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="M18" s="5" t="inlineStr">
+        <is>
           <t>DoW Enterprise</t>
         </is>
       </c>
-      <c r="M18" s="5" t="inlineStr"/>
       <c r="N18" s="5" t="inlineStr"/>
       <c r="O18" s="5" t="inlineStr"/>
       <c r="P18" s="5" t="inlineStr"/>

--- a/demo/workbooks/DEMO_NIST_800-53r5_Example System.xlsx
+++ b/demo/workbooks/DEMO_NIST_800-53r5_Example System.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U22"/>
+  <dimension ref="A1:U23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1734,44 +1734,44 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>AU-4</t>
+          <t>PE-8</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Audit Log Storage Capacity</t>
+          <t>Visitor Access Records</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr"/>
       <c r="E19" s="5" t="inlineStr"/>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>Audit log storage capacity for the Example System Demo SIEM tier is documented in the Audit Log Storage Capacity Memo (USD20240623). The memo is a draft whose capacity sections are not yet reconciled.</t>
+          <t>Visitor access records for the Example System Demo are inherited on the cloud enclaves — AWS GovCloud and Azure Government maintain visitor access logs for their own datacenters — but the on-premises/workbook footprint is a customer responsibility (Column L = local assessment) and the program has not yet produced a visitor-access log for the on-prem facility.</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>AU-4</t>
+          <t>PE-8</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>CCI-000137</t>
+          <t>CCI-000174</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>The organization allocates audit log storage capacity to accommodate the organization-defined audit log retention requirements.</t>
+          <t>The organization maintains visitor access records to the facility where the information system resides.</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>Provide the audit storage capacity allocation and a utilization analysis demonstrating the retention period is met.</t>
+          <t>Cite the provider CRM for each cloud enclave; for the on-premises footprint provide the visitor-access log and its retention/review procedure, or document the scope exclusion.</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>Examine the allocated capacity against the 1-year retention requirement and the measured ingest/utilization rate.</t>
+          <t>Examine provider CRM inheritance for each cloud enclave and assess the on-premises visitor-access records for the flex scope.</t>
         </is>
       </c>
       <c r="L19" s="5" t="inlineStr">
@@ -1809,44 +1809,44 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>AU-6</t>
+          <t>AU-4</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Audit Record Review, Analysis, and Reporting</t>
+          <t>Audit Log Storage Capacity</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr"/>
       <c r="E20" s="5" t="inlineStr"/>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>Audit record review for the Example System Demo differs by cloud: the AWS GovCloud enclave shares review between the provider SOC and the customer, while the Azure Government enclave is reviewed end-to-end by the customer's Microsoft Sentinel workspace.</t>
+          <t>Audit log storage capacity for the Example System Demo SIEM tier is documented in the Audit Log Storage Capacity Memo (USD20240623). The memo is a draft whose capacity sections are not yet reconciled.</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>AU-6</t>
+          <t>AU-4</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>CCI-000148</t>
+          <t>CCI-000137</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>The organization reviews and analyzes information system audit records for indications of inappropriate or unusual activity.</t>
+          <t>The organization allocates audit log storage capacity to accommodate the organization-defined audit log retention requirements.</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>Provide the audit-review cadence and sample findings for each cloud enclave; cite the provider-shared review where applicable.</t>
+          <t>Provide the audit storage capacity allocation and a utilization analysis demonstrating the retention period is met.</t>
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>Examine the audit-review process per scope. For the customer-owned scope verify the SIEM review cadence; for the shared scope confirm the provider/customer review split.</t>
+          <t>Examine the allocated capacity against the 1-year retention requirement and the measured ingest/utilization rate.</t>
         </is>
       </c>
       <c r="L20" s="5" t="inlineStr">
@@ -1884,44 +1884,44 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>SC-13</t>
+          <t>AU-6</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Cryptographic Protection</t>
+          <t>Audit Record Review, Analysis, and Reporting</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr"/>
       <c r="E21" s="5" t="inlineStr"/>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>Cryptographic protection for the Example System Demo differs by cloud: the AWS GovCloud enclave shares responsibility (customer selects FIPS endpoints and guest-OS FIPS mode), while the Azure Government enclave consumes only Microsoft-provided FIPS 140-2 validated modules and fully inherits the control.</t>
+          <t>Audit record review for the Example System Demo differs by cloud: the AWS GovCloud enclave shares review between the provider SOC and the customer, while the Azure Government enclave is reviewed end-to-end by the customer's Microsoft Sentinel workspace.</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>SC-13</t>
+          <t>AU-6</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>CCI-002450</t>
+          <t>CCI-000148</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>The information system implements organization-defined cryptographic uses and type of cryptography in accordance with applicable laws.</t>
+          <t>The organization reviews and analyzes information system audit records for indications of inappropriate or unusual activity.</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>Provide the FIPS-validated module configuration per cloud enclave; cite the provider CRM where the control is inherited.</t>
+          <t>Provide the audit-review cadence and sample findings for each cloud enclave; cite the provider-shared review where applicable.</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>Examine the cryptographic implementation per scope. For the shared scope verify FIPS endpoint/guest-OS configuration; for the inherited scope confirm the provider supplies the validated modules.</t>
+          <t>Examine the audit-review process per scope. For the customer-owned scope verify the SIEM review cadence; for the shared scope confirm the provider/customer review split.</t>
         </is>
       </c>
       <c r="L21" s="5" t="inlineStr">
@@ -1959,44 +1959,44 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>AU-9</t>
+          <t>SC-13</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Protection of Audit Information</t>
+          <t>Cryptographic Protection</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr"/>
       <c r="E22" s="5" t="inlineStr"/>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>Protection of audit information for the Example System Demo is customer-owned on both cloud enclaves; immutability and access controls on the customer log stores are documented in the Audit Information Protection Memo (USD20240624), a draft whose protection sections are not yet reconciled.</t>
+          <t>Cryptographic protection for the Example System Demo differs by cloud: the AWS GovCloud enclave shares responsibility (customer selects FIPS endpoints and guest-OS FIPS mode), while the Azure Government enclave consumes only Microsoft-provided FIPS 140-2 validated modules and fully inherits the control.</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>AU-9</t>
+          <t>SC-13</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>CCI-001493</t>
+          <t>CCI-002450</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>The information system protects audit information and audit tools from unauthorized access, modification, and deletion.</t>
+          <t>The information system implements organization-defined cryptographic uses and type of cryptography in accordance with applicable laws.</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>Provide the immutability / access-control configuration for the customer audit log stores on each cloud enclave.</t>
+          <t>Provide the FIPS-validated module configuration per cloud enclave; cite the provider CRM where the control is inherited.</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>Examine the configured object-lock / immutable-retention and access controls on the customer log stores against the protection requirement; confirm the as-configured state matches the memo.</t>
+          <t>Examine the cryptographic implementation per scope. For the shared scope verify FIPS endpoint/guest-OS configuration; for the inherited scope confirm the provider supplies the validated modules.</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr">
@@ -2026,13 +2026,88 @@
       </c>
       <c r="U22" s="5" t="inlineStr"/>
     </row>
+    <row r="23" ht="110" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>AU-9</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Protection of Audit Information</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr"/>
+      <c r="E23" s="5" t="inlineStr"/>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>Protection of audit information for the Example System Demo is customer-owned on both cloud enclaves; immutability and access controls on the customer log stores are documented in the Audit Information Protection Memo (USD20240624), a draft whose protection sections are not yet reconciled.</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>AU-9</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>CCI-001493</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>The information system protects audit information and audit tools from unauthorized access, modification, and deletion.</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>Provide the immutability / access-control configuration for the customer audit log stores on each cloud enclave.</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>Examine the configured object-lock / immutable-retention and access controls on the customer log stores against the protection requirement; confirm the as-configured state matches the memo.</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="inlineStr"/>
+      <c r="N23" s="5" t="inlineStr"/>
+      <c r="O23" s="5" t="inlineStr"/>
+      <c r="P23" s="5" t="inlineStr"/>
+      <c r="Q23" s="5" t="inlineStr"/>
+      <c r="R23" s="5" t="inlineStr">
+        <is>
+          <t>NIST SP 800-53 Rev. 5</t>
+        </is>
+      </c>
+      <c r="S23" s="5" t="inlineStr">
+        <is>
+          <t>System-Specific</t>
+        </is>
+      </c>
+      <c r="T23" s="5" t="inlineStr">
+        <is>
+          <t>T. Prior</t>
+        </is>
+      </c>
+      <c r="U23" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A5:U5"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="N7:N22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid status" error="Status must be Compliant, Non-Compliant, or Not Applicable." type="list">
+    <dataValidation sqref="N7:N23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid status" error="Status must be Compliant, Non-Compliant, or Not Applicable." type="list">
       <formula1>"Compliant,Non-Compliant,Not Applicable"</formula1>
     </dataValidation>
   </dataValidations>
